--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486407_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486407_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9759</v>
+        <v>7.8999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1136</v>
+        <v>4.8527</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8623</v>
+        <v>3.0472</v>
       </c>
       <c r="G2" t="n">
         <v>4.0049</v>
@@ -610,13 +610,13 @@
         <v>3.4801</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8343</v>
+        <v>-0.9103</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.8494</v>
+        <v>-1.1103</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0151</v>
+        <v>0.2001</v>
       </c>
       <c r="V2" t="n">
         <v>1.3252</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8816</v>
+        <v>7.1207</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3255</v>
+        <v>4.133</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5562</v>
+        <v>2.9877</v>
       </c>
       <c r="G3" t="n">
         <v>4.0191</v>
@@ -688,13 +688,13 @@
         <v>2.6101</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.3104</v>
+        <v>-1.0713</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.7809</v>
+        <v>-0.9734</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5295</v>
+        <v>-0.098</v>
       </c>
       <c r="V3" t="n">
         <v>2.6504</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0339</v>
+        <v>1.5745</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4291</v>
+        <v>-1.2905</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6048</v>
+        <v>2.865</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0268</v>
@@ -766,13 +766,13 @@
         <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3859</v>
+        <v>0.9265</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6788</v>
+        <v>-0.0408</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7071</v>
+        <v>0.9673</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1952</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3083</v>
+        <v>-0.2987</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.757</v>
+        <v>-0.1862</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0653</v>
+        <v>-0.1125</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6733</v>
+        <v>0.1051</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.2479</v>
+        <v>-0.3802</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5746</v>
+        <v>0.4853</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9337</v>
+        <v>0.0565</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.1011</v>
+        <v>0.0182</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1674</v>
+        <v>0.0382</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7397</v>
+        <v>0.0486</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1468</v>
+        <v>-0.3985</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4072</v>
+        <v>0.447</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3926</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1935</v>
+        <v>-0.1863</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3942</v>
+        <v>-0.0252</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5876</v>
+        <v>-0.161</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2872</v>
+        <v>-0.4056</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.298</v>
+        <v>-1.4708</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0108</v>
+        <v>1.0653</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1051</v>
+        <v>-1.6733</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3802</v>
+        <v>-3.2479</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4853</v>
+        <v>1.5746</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0565</v>
+        <v>-0.9337</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0182</v>
+        <v>-2.1011</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0382</v>
+        <v>1.1674</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0486</v>
+        <v>-0.7397</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3985</v>
+        <v>-1.1468</v>
       </c>
       <c r="O6" t="n">
-        <v>0.447</v>
+        <v>0.4072</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2175</v>
+        <v>2.1751</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1747</v>
+        <v>-0.9073</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.137</v>
+        <v>-0.3196</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0377</v>
+        <v>-0.5876</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>M. AYESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0502</v>
+        <v>-1.3859</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1846</v>
+        <v>-0.8388</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8656</v>
+        <v>-0.5471</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1068</v>
+        <v>-1.1945</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.506</v>
+        <v>-0.067</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3992</v>
+        <v>-1.1275</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4652</v>
+        <v>-0.7451</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.5417</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>-0.7451</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6417</v>
+        <v>-0.4495</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9643</v>
+        <v>-0.067</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3227</v>
+        <v>-0.3825</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8391</v>
+        <v>-0.1914</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3257</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5135</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. AYESA RODRIGUEZ</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5285</v>
+        <v>-1.818</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9505</v>
+        <v>-0.9203</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5779</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1945</v>
+        <v>2.0729</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.067</v>
+        <v>-0.14</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1275</v>
+        <v>2.2129</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7451</v>
+        <v>1.4555</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.2857</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7451</v>
+        <v>1.7412</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4495</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.067</v>
+        <v>0.1457</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3825</v>
+        <v>0.4717</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.4801</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.334</v>
+        <v>-0.7381</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2055</v>
+        <v>-0.7859</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1285</v>
+        <v>0.0478</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.6504</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5285</v>
+        <v>-2.0699</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.43</v>
+        <v>-1.0947</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0985</v>
+        <v>-0.9752</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1687</v>
@@ -1156,13 +1156,13 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1423</v>
+        <v>-0.6838</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9589</v>
+        <v>-0.6237</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1834</v>
+        <v>-0.0601</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8576</v>
+        <v>-2.1762</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4359</v>
+        <v>-0.7867</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4217</v>
+        <v>-1.3896</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0729</v>
+        <v>-2.1068</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.14</v>
+        <v>-2.506</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2129</v>
+        <v>0.3992</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4555</v>
+        <v>-1.4652</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2857</v>
+        <v>-1.5417</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7412</v>
+        <v>0.0765</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6173999999999999</v>
+        <v>-0.6417</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1457</v>
+        <v>-0.9643</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4717</v>
+        <v>0.3227</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3926</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4801</v>
+        <v>-1.305</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7777</v>
+        <v>-0.2869</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3014</v>
+        <v>-0.2764</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4762</v>
+        <v>-0.0105</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8902</v>
+        <v>2.2599</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6504</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2024</v>
+        <v>-3.2523</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6652</v>
+        <v>-5.7459</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4628</v>
+        <v>2.4936</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4234</v>
@@ -1312,13 +1312,13 @@
         <v>3.2626</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6066</v>
+        <v>-0.6564</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.0549</v>
+        <v>-1.1356</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4483</v>
+        <v>0.4792</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2599</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3221</v>
+        <v>-4.0802</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1009</v>
+        <v>-3.9206</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2213</v>
+        <v>-0.1596</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7156</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6919</v>
+        <v>-0.45</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4795</v>
+        <v>-0.2992</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2125</v>
+        <v>-0.1508</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7395</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4231999999999996</v>
+        <v>1.108299999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.9539</v>
+        <v>-7.268800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>8.3772</v>
+        <v>8.377100000000002</v>
       </c>
       <c r="G13" t="n">
         <v>1.892900000000002</v>
@@ -1450,13 +1450,13 @@
         <v>4.2235</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2963000000000002</v>
+        <v>-0.2963000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3015999999999999</v>
+        <v>0.3016000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.598</v>
+        <v>-0.5980000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>4.35</v>
@@ -1468,13 +1468,13 @@
         <v>17.4005</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.840400000000001</v>
+        <v>-5.1553</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.368799999999999</v>
+        <v>-5.683800000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5285999999999998</v>
+        <v>0.5287999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.02079999999999993</v>
@@ -1483,7 +1483,7 @@
         <v>9.276400000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.255699999999999</v>
+        <v>-9.255700000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4278</v>
+        <v>4.1137</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5205</v>
+        <v>3.5147</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9073</v>
+        <v>0.5991</v>
       </c>
       <c r="G14" t="n">
         <v>2.7334</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5416</v>
+        <v>1.2275</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4132</v>
+        <v>0.4074</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1284</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9347</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5883</v>
+        <v>2.9852</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3001</v>
+        <v>1.6354</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2881</v>
+        <v>1.3498</v>
       </c>
       <c r="G15" t="n">
         <v>1.6892</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0291</v>
+        <v>0.426</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9589</v>
+        <v>-0.6237</v>
       </c>
       <c r="U15" t="n">
-        <v>0.988</v>
+        <v>1.0497</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5679</v>
+        <v>1.9301</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0148</v>
+        <v>0.3196</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5531</v>
+        <v>1.6105</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8985</v>
+        <v>0.7791</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1216</v>
+        <v>-0.1428</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7769</v>
+        <v>0.922</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5218</v>
+        <v>0.203</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1246</v>
+        <v>-0.8879</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6463</v>
+        <v>1.0909</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6233</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2461</v>
+        <v>0.7451</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8694</v>
+        <v>-0.1689</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7776</v>
+        <v>0.2809</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6682</v>
+        <v>0.1166</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1095</v>
+        <v>0.1643</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4522</v>
+        <v>1.2635</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1274</v>
+        <v>-0.3204</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5796</v>
+        <v>1.5839</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7791</v>
+        <v>0.8985</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1428</v>
+        <v>0.1216</v>
       </c>
       <c r="I17" t="n">
-        <v>0.922</v>
+        <v>0.7769</v>
       </c>
       <c r="J17" t="n">
-        <v>0.203</v>
+        <v>1.5218</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8879</v>
+        <v>-0.1246</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0909</v>
+        <v>1.6463</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.6233</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7451</v>
+        <v>0.2461</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1689</v>
+        <v>-0.8694</v>
       </c>
       <c r="P17" t="n">
-        <v>0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.197</v>
+        <v>0.4732</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3305</v>
+        <v>0.3329</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1335</v>
+        <v>0.1403</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ALONSO CUEVAS</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3784</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2007</v>
+        <v>-2.1712</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8223</v>
+        <v>2.9681</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8087</v>
+        <v>0.9547</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2891</v>
+        <v>-0.3378</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5195</v>
+        <v>1.2925</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1384</v>
+        <v>0.4353</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1277</v>
+        <v>-0.5991</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2661</v>
+        <v>1.0343</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6703</v>
+        <v>0.5194</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4169</v>
+        <v>0.2612</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2534</v>
+        <v>0.2582</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0875</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6645</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2091</v>
+        <v>-0.4314</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4554</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.3698</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.695</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>A. ALONSO CUEVAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3498</v>
+        <v>0.2667</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6182</v>
+        <v>1.0889</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9681</v>
+        <v>-0.8223</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9547</v>
+        <v>-0.8087</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3378</v>
+        <v>-0.2891</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2925</v>
+        <v>-0.5195</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4353</v>
+        <v>-0.1384</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5991</v>
+        <v>0.1277</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0343</v>
+        <v>-0.2661</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5194</v>
+        <v>-0.6703</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2612</v>
+        <v>-0.4169</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2582</v>
+        <v>-0.2534</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.0875</v>
+        <v>1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.113</v>
+        <v>0.5528</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8784</v>
+        <v>0.0973</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.4554</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3698</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3698</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4356</v>
+        <v>-0.1273</v>
       </c>
       <c r="E20" t="n">
         <v>0.3054</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7409</v>
+        <v>-0.4327</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8344</v>
@@ -2014,13 +2014,13 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3184</v>
+        <v>-0.0102</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4074</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.3972</v>
       </c>
       <c r="V20" t="n">
         <v>0.9347</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3603</v>
+        <v>-1.2655</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4326</v>
+        <v>-1.852</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9277</v>
+        <v>0.5865</v>
       </c>
       <c r="G21" t="n">
-        <v>3.4447</v>
+        <v>-0.5371</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9897</v>
+        <v>-0.1825</v>
       </c>
       <c r="I21" t="n">
-        <v>0.455</v>
+        <v>-0.3546</v>
       </c>
       <c r="J21" t="n">
-        <v>3.503</v>
+        <v>-0.3871</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4121</v>
+        <v>-1.1553</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0909</v>
+        <v>0.7682</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0583</v>
+        <v>-0.15</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5776</v>
+        <v>0.9728</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6359</v>
+        <v>-1.1228</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.6976</v>
+        <v>0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1525</v>
+        <v>-0.2064</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4146</v>
+        <v>-0.7679</v>
       </c>
       <c r="U21" t="n">
-        <v>0.738</v>
+        <v>0.5615</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2599</v>
+        <v>-0.7395</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7286</v>
+        <v>-1.7495</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1062</v>
+        <v>-0.5443</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3776</v>
+        <v>-1.2051</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.009</v>
+        <v>3.4447</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1489</v>
+        <v>2.9897</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1578</v>
+        <v>0.455</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4566</v>
+        <v>3.503</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3832</v>
+        <v>2.4121</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8399</v>
+        <v>1.0909</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5523</v>
+        <v>-0.0583</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2344</v>
+        <v>0.5776</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.318</v>
+        <v>-0.6359</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3926</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2626</v>
+        <v>-4.3501</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7382</v>
+        <v>0.7634</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4831</v>
+        <v>0.3028</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2551</v>
+        <v>0.4605</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9347</v>
+        <v>-2.2599</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1952</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3984</v>
+        <v>-1.8596</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5226</v>
+        <v>-2.3297</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1242</v>
+        <v>0.4701</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5371</v>
+        <v>-1.009</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1825</v>
+        <v>0.1489</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3546</v>
+        <v>-1.1578</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3871</v>
+        <v>-0.4566</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1553</v>
+        <v>0.3832</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7682</v>
+        <v>-0.8399</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.15</v>
+        <v>-0.5523</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9728</v>
+        <v>-0.2344</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1228</v>
+        <v>-0.318</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R23" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3393</v>
+        <v>0.6072</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4384</v>
+        <v>0.2596</v>
       </c>
       <c r="U23" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.3476</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7395</v>
+        <v>0.9347</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9724</v>
+        <v>-3.3271</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9802</v>
+        <v>-4.5963</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0078</v>
+        <v>1.2692</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5479</v>
+        <v>-5.6553</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9247</v>
+        <v>-2.8799</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.6233</v>
+        <v>-2.7754</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.4903</v>
+        <v>-5.2806</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5229</v>
+        <v>-2.9921</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9674</v>
+        <v>-2.2885</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0576</v>
+        <v>-0.3747</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4018</v>
+        <v>0.1122</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6558</v>
+        <v>-0.4869</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>1.228</v>
+        <v>0.4158</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5552</v>
+        <v>0.0769</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6728</v>
+        <v>0.3389</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.2925</v>
+        <v>-3.4503</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9316</v>
+        <v>-3.4272</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6391</v>
+        <v>-0.0231</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.6553</v>
+        <v>-3.5479</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.8799</v>
+        <v>-0.9247</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.7754</v>
+        <v>-2.6233</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.2806</v>
+        <v>-2.4903</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.9921</v>
+        <v>-0.5229</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.2885</v>
+        <v>-1.9674</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3747</v>
+        <v>-1.0576</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1122</v>
+        <v>-0.4018</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4869</v>
+        <v>-0.6558</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R25" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4504</v>
+        <v>0.7502</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2584</v>
+        <v>0.1082</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7087</v>
+        <v>0.642</v>
       </c>
       <c r="V25" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="26">
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4234</v>
+        <v>-0.4231999999999996</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.377299999999998</v>
+        <v>-8.377099999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>7.954000000000001</v>
+        <v>7.954</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.8928</v>
+        <v>-1.892800000000001</v>
       </c>
       <c r="H26" t="n">
         <v>1.7331</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.6256</v>
+        <v>-3.625599999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.296400000000002</v>
+        <v>0.2964000000000016</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3016999999999994</v>
+        <v>-0.3017</v>
       </c>
       <c r="L26" t="n">
         <v>0.5977999999999999</v>
@@ -2482,19 +2482,19 @@
         <v>13.05</v>
       </c>
       <c r="S26" t="n">
-        <v>5.8402</v>
+        <v>5.840399999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5285999999999997</v>
+        <v>-0.5287000000000003</v>
       </c>
       <c r="U26" t="n">
-        <v>6.368799999999999</v>
+        <v>6.3689</v>
       </c>
       <c r="V26" t="n">
         <v>-0.02060000000000017</v>
       </c>
       <c r="W26" t="n">
-        <v>9.255699999999999</v>
+        <v>9.255700000000001</v>
       </c>
       <c r="X26" t="n">
         <v>-9.276299999999999</v>
